--- a/worked_example/data/constraints.xlsx
+++ b/worked_example/data/constraints.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://southwestacademichealthscie-my.sharepoint.com/personal/richard_blackwell_healthinnovationsouthwest_com/Documents/Workspace/intersectionality_using_ipf/worked_example/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DEAB096-6DCD-4AE3-8039-FA9CA89401C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{6DEAB096-6DCD-4AE3-8039-FA9CA89401C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69666369-5EC7-4E26-ACF8-77A04A25E8A2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{1A2FE70F-3E70-4C33-87E6-9C4983C1D1CB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1A2FE70F-3E70-4C33-87E6-9C4983C1D1CB}"/>
   </bookViews>
   <sheets>
     <sheet name="AGE_HEALTH" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="16">
   <si>
     <t>E07000043</t>
   </si>
@@ -80,9 +80,6 @@
   </si>
   <si>
     <t>HEALTH</t>
-  </si>
-  <si>
-    <t>NA</t>
   </si>
   <si>
     <t>GOOD</t>
@@ -463,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F9858B5-4353-4C6C-80C7-50C1F3FFD63A}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -497,7 +494,7 @@
         <v>13</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15943</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -514,7 +511,7 @@
         <v>14</v>
       </c>
       <c r="E3">
-        <v>15943</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -531,7 +528,7 @@
         <v>15</v>
       </c>
       <c r="E4">
-        <v>355</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -542,13 +539,13 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E5">
-        <v>76</v>
+        <v>47299</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -562,10 +559,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -579,10 +576,10 @@
         <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>47299</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -593,13 +590,13 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E8">
-        <v>6190</v>
+        <v>15292</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -610,13 +607,13 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E9">
-        <v>2531</v>
+        <v>6797</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -630,60 +627,9 @@
         <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11">
-        <v>15292</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12">
-        <v>6797</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13">
         <v>2633</v>
       </c>
     </row>
@@ -823,7 +769,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4172E31F-D086-432E-8BBA-D6C7B56274BE}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -864,7 +810,7 @@
         <v>7</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>40151</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -881,7 +827,7 @@
         <v>8</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>38383</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -898,7 +844,7 @@
         <v>7</v>
       </c>
       <c r="E4">
-        <v>40151</v>
+        <v>6958</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -915,7 +861,7 @@
         <v>8</v>
       </c>
       <c r="E5">
-        <v>38383</v>
+        <v>6384</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -932,7 +878,7 @@
         <v>7</v>
       </c>
       <c r="E6">
-        <v>6958</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -949,40 +895,6 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>6384</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8">
-        <v>2776</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9">
         <v>2464</v>
       </c>
     </row>
